--- a/data/trans_bre/P1804_2016_2023-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P1804_2016_2023-Habitat-trans_bre.xlsx
@@ -578,7 +578,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2,79</t>
+          <t>2,93</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>79,53%</t>
+          <t>82,17%</t>
         </is>
       </c>
     </row>
@@ -601,22 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 4,69</t>
+          <t>-0,17; 4,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,13; 5,25</t>
+          <t>0,18; 5,49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,42; 139,81</t>
+          <t>-6,43; 133,46</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 219,96</t>
+          <t>-2,14; 234,04</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2,7</t>
+          <t>0,42</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>45,09%</t>
+          <t>4,94%</t>
         </is>
       </c>
     </row>
@@ -661,22 +661,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,93; 5,5</t>
+          <t>0,74; 5,42</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 6,09</t>
+          <t>-2,39; 3,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12,12; 118,09</t>
+          <t>8,2; 112,9</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,37; 170,42</t>
+          <t>-23,73; 45,94</t>
         </is>
       </c>
     </row>
@@ -698,7 +698,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1,33</t>
+          <t>3,11</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>46,99%</t>
+          <t>102,27%</t>
         </is>
       </c>
     </row>
@@ -721,22 +721,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,5; 9,24</t>
+          <t>3,53; 9,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 3,32</t>
+          <t>1,31; 5,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>51,58; 225,04</t>
+          <t>50,72; 213,63</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-32,96; 144,34</t>
+          <t>29,99; 229,41</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1,94</t>
+          <t>3,07</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>37,77%</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,16; 5,9</t>
+          <t>0,26; 6,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 4,54</t>
+          <t>0,94; 5,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,04; 76,07</t>
+          <t>2,19; 76,66</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,09; 63,35</t>
+          <t>10,2; 78,04</t>
         </is>
       </c>
     </row>
@@ -818,7 +818,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2,05</t>
+          <t>2,34</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>37,81%</t>
         </is>
       </c>
     </row>
@@ -841,22 +841,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,38; 4,98</t>
+          <t>2,17; 4,92</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,58; 3,76</t>
+          <t>1,07; 3,51</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>33,36; 87,3</t>
+          <t>31,87; 88,4</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9,0; 81,83</t>
+          <t>15,88; 64,21</t>
         </is>
       </c>
     </row>
